--- a/見積依頼/FC蒲田計画/FC蒲田計画_照明器具_見積依頼.xlsx
+++ b/見積依頼/FC蒲田計画/FC蒲田計画_照明器具_見積依頼.xlsx
@@ -439,26 +439,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>品番</t>
+          <t>品名</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>商品名</t>
+          <t>型番・規格</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -478,19 +481,34 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>見積単価</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>発注単価</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>備考</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>予算カテゴリー</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>ダウンライト</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>XAD11002K CQ1</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>ダウンライト（B）</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -507,16 +525,27 @@
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>記号B 2700K ホワイトつや消し</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>照明器具</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>ダウンライト</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>XED1130LCE1</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>ダウンライト（C）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -533,16 +562,27 @@
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>記号C 2700K ホワイトつや消し</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>照明器具</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>ブラケット</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>OB081016LR</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>ブラケット（D）</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -559,16 +599,27 @@
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>記号D 2700K マットホワイト</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>照明器具</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>キッチン照明</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>AB38553L</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>キッチン照明（F）</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -584,21 +635,28 @@
           <t>台</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>非調光</t>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>記号F 5000K 非調光</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>照明器具</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>非常照明</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>NWCF59511LE1</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>非常照明（G）</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -615,16 +673,27 @@
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>記号G 2700K ブラック</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>防災設備（自火報・非常照明）</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>避難口誘導灯</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>OR037535</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>避難口誘導灯（H）</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -641,16 +710,27 @@
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>記号H</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>防災設備（自火報・非常照明）</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>非常灯</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>AR50616</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>非常灯（a1）</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -667,6 +747,17 @@
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>記号a1</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>防災設備（自火報・非常照明）</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
